--- a/results/by_outcome/full_results_education_PGI_Brothers.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Brothers.xlsx
@@ -474,32 +474,32 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>0.61921597256992</v>
+        <v>0.62315228306135</v>
       </c>
       <c r="D2" t="n">
-        <v>0.38118740130876</v>
+        <v>0.377246921038046</v>
       </c>
       <c r="E2" t="n">
-        <v>1.00040337387868</v>
+        <v>1.0003992040994</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="n">
-        <v>0.381033702266369</v>
+        <v>0.377096382616238</v>
       </c>
       <c r="K2" t="n">
-        <v>0.339269321978875</v>
+        <v>0.335559196922099</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0177987076880658</v>
+        <v>0.0156374652188288</v>
       </c>
       <c r="M2" t="n">
-        <v>0.050851559352711</v>
+        <v>0.048675943136103</v>
       </c>
       <c r="N2" t="n">
-        <v>0.357068029666941</v>
+        <v>0.351196662140928</v>
       </c>
       <c r="O2"/>
     </row>
@@ -514,10 +514,10 @@
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.586149788248297</v>
+        <v>0.590100616048253</v>
       </c>
       <c r="G3" t="n">
-        <v>0.339406174361199</v>
+        <v>0.3356931535291</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -541,10 +541,10 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.568343901026476</v>
+        <v>0.574456908289205</v>
       </c>
       <c r="I4" t="n">
-        <v>0.370100022661873</v>
+        <v>0.362355795446283</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -552,7 +552,7 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.43188526161908</v>
+        <v>0.425772325752341</v>
       </c>
     </row>
   </sheetData>
@@ -597,13 +597,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.381033702266369</v>
+        <v>0.377096382616238</v>
       </c>
       <c r="D2" t="n">
-        <v>0.317993247047481</v>
+        <v>0.311681329455949</v>
       </c>
       <c r="E2" t="n">
-        <v>0.444256084137405</v>
+        <v>0.439403286843348</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -620,16 +620,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.357068029666941</v>
+        <v>0.351196662140928</v>
       </c>
       <c r="D3" t="n">
-        <v>0.256330855518621</v>
+        <v>0.261381682057821</v>
       </c>
       <c r="E3" t="n">
-        <v>0.480462937544723</v>
+        <v>0.471594314306167</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000000000245617526317687</v>
+        <v>0.000000000114181109012179</v>
       </c>
       <c r="G3" t="n">
         <v>946</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.43188526161908</v>
+        <v>0.425772325752341</v>
       </c>
       <c r="D4" t="n">
-        <v>0.333783508883774</v>
+        <v>0.352815096995119</v>
       </c>
       <c r="E4" t="n">
-        <v>0.547520414299915</v>
+        <v>0.541818320859761</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0000000000000021094237467878</v>
+        <v>0.000000000000000222044604925031</v>
       </c>
       <c r="G4" t="n">
         <v>946</v>
@@ -666,16 +666,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0748172319521389</v>
+        <v>0.0745756636114136</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0363744670253994</v>
+        <v>0.0301169247030731</v>
       </c>
       <c r="E5" t="n">
-        <v>0.116621779972593</v>
+        <v>0.102354009931112</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000122255881159661</v>
+        <v>0.0000648704293882973</v>
       </c>
       <c r="G5" t="n">
         <v>946</v>

--- a/results/by_outcome/full_results_education_PGI_Brothers.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Brothers.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Outcome</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t xml:space="preserve">Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">Lower</t>
@@ -588,6 +591,9 @@
       <c r="G1" t="s">
         <v>24</v>
       </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -600,15 +606,18 @@
         <v>0.377096382616238</v>
       </c>
       <c r="D2" t="n">
-        <v>0.311681329455949</v>
+        <v>0.0333240499649498</v>
       </c>
       <c r="E2" t="n">
-        <v>0.439403286843348</v>
+        <v>0.319660829406561</v>
       </c>
       <c r="F2" t="n">
+        <v>0.433969943788578</v>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>946</v>
       </c>
     </row>
@@ -623,15 +632,18 @@
         <v>0.351196662140928</v>
       </c>
       <c r="D3" t="n">
-        <v>0.261381682057821</v>
+        <v>0.0550412039682858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.471594314306167</v>
+        <v>0.249634739825339</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000000000114181109012179</v>
+        <v>0.461734389446873</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>946</v>
       </c>
     </row>
@@ -646,21 +658,24 @@
         <v>0.425772325752341</v>
       </c>
       <c r="D4" t="n">
-        <v>0.352815096995119</v>
+        <v>0.055108722411546</v>
       </c>
       <c r="E4" t="n">
-        <v>0.541818320859761</v>
+        <v>0.332892421893397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000000000000000222044604925031</v>
+        <v>0.538968779689618</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>946</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -669,15 +684,18 @@
         <v>0.0745756636114136</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0301169247030731</v>
+        <v>0.0221040472646979</v>
       </c>
       <c r="E5" t="n">
-        <v>0.102354009931112</v>
+        <v>0.0318450421168323</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0000648704293882973</v>
+        <v>0.118055803785499</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>946</v>
       </c>
     </row>

--- a/results/by_outcome/full_results_education_PGI_Brothers.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Brothers.xlsx
@@ -606,13 +606,13 @@
         <v>0.377096382616238</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0333240499649498</v>
+        <v>0.0316056183531153</v>
       </c>
       <c r="E2" t="n">
-        <v>0.319660829406561</v>
+        <v>0.317740053272521</v>
       </c>
       <c r="F2" t="n">
-        <v>0.433969943788578</v>
+        <v>0.439845979672591</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -632,16 +632,16 @@
         <v>0.351196662140928</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0550412039682858</v>
+        <v>0.0560182179415059</v>
       </c>
       <c r="E3" t="n">
-        <v>0.249634739825339</v>
+        <v>0.248201922992115</v>
       </c>
       <c r="F3" t="n">
-        <v>0.461734389446873</v>
+        <v>0.470041466088303</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.000000000181303083657269</v>
       </c>
       <c r="H3" t="n">
         <v>946</v>
@@ -658,16 +658,16 @@
         <v>0.425772325752341</v>
       </c>
       <c r="D4" t="n">
-        <v>0.055108722411546</v>
+        <v>0.0547564954997356</v>
       </c>
       <c r="E4" t="n">
-        <v>0.332892421893397</v>
+        <v>0.326524700446147</v>
       </c>
       <c r="F4" t="n">
-        <v>0.538968779689618</v>
+        <v>0.539806977804654</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.00000000000000377475828372553</v>
       </c>
       <c r="H4" t="n">
         <v>946</v>
@@ -684,16 +684,16 @@
         <v>0.0745756636114136</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0221040472646979</v>
+        <v>0.019779696832997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0318450421168323</v>
+        <v>0.0343562651326355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.118055803785499</v>
+        <v>0.112446169927595</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.0000815212104267049</v>
       </c>
       <c r="H5" t="n">
         <v>946</v>

--- a/results/by_outcome/full_results_education_PGI_Brothers.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Brothers.xlsx
@@ -493,16 +493,16 @@
         <v>0.377096382616238</v>
       </c>
       <c r="K2" t="n">
-        <v>0.335559196922099</v>
+        <v>0.331260036216921</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0156374652188288</v>
+        <v>0.00777196734886643</v>
       </c>
       <c r="M2" t="n">
-        <v>0.048675943136103</v>
+        <v>0.0461093912250932</v>
       </c>
       <c r="N2" t="n">
-        <v>0.351196662140928</v>
+        <v>0.339032003565788</v>
       </c>
       <c r="O2"/>
     </row>
@@ -517,10 +517,10 @@
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.590100616048253</v>
+        <v>0.584799554728351</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3356931535291</v>
+        <v>0.331392276581345</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -544,10 +544,10 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.574456908289205</v>
+        <v>0.577024484778259</v>
       </c>
       <c r="I4" t="n">
-        <v>0.362355795446283</v>
+        <v>0.33238972852208</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -555,7 +555,7 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.425772325752341</v>
+        <v>0.423205773841332</v>
       </c>
     </row>
   </sheetData>
@@ -606,13 +606,13 @@
         <v>0.377096382616238</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0316056183531153</v>
+        <v>0.0320942684678203</v>
       </c>
       <c r="E2" t="n">
-        <v>0.317740053272521</v>
+        <v>0.313141886300811</v>
       </c>
       <c r="F2" t="n">
-        <v>0.439845979672591</v>
+        <v>0.438412801294494</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -629,19 +629,19 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.351196662140928</v>
+        <v>0.339032003565788</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0560182179415059</v>
+        <v>0.0516407500594495</v>
       </c>
       <c r="E3" t="n">
-        <v>0.248201922992115</v>
+        <v>0.251630257505263</v>
       </c>
       <c r="F3" t="n">
-        <v>0.470041466088303</v>
+        <v>0.44781872690609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000000000181303083657269</v>
+        <v>0.0000000000259809951330681</v>
       </c>
       <c r="H3" t="n">
         <v>946</v>
@@ -655,19 +655,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.425772325752341</v>
+        <v>0.423205773841332</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0547564954997356</v>
+        <v>0.0502264571493261</v>
       </c>
       <c r="E4" t="n">
-        <v>0.326524700446147</v>
+        <v>0.332552472256815</v>
       </c>
       <c r="F4" t="n">
-        <v>0.539806977804654</v>
+        <v>0.530268889581896</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00000000000000377475828372553</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>946</v>
@@ -681,19 +681,19 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0745756636114136</v>
+        <v>0.0841737702755438</v>
       </c>
       <c r="D5" t="n">
-        <v>0.019779696832997</v>
+        <v>0.018194123510265</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0343562651326355</v>
+        <v>0.0498218903111359</v>
       </c>
       <c r="F5" t="n">
-        <v>0.112446169927595</v>
+        <v>0.120688704541321</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0000815212104267049</v>
+        <v>0.00000186014643799304</v>
       </c>
       <c r="H5" t="n">
         <v>946</v>

--- a/results/by_outcome/full_results_education_PGI_Brothers.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Brothers.xlsx
@@ -493,16 +493,16 @@
         <v>0.377096382616238</v>
       </c>
       <c r="K2" t="n">
-        <v>0.331260036216921</v>
+        <v>0.341206051864366</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00777196734886643</v>
+        <v>0.00489598811502636</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0461093912250932</v>
+        <v>0.0431231792647801</v>
       </c>
       <c r="N2" t="n">
-        <v>0.339032003565788</v>
+        <v>0.346102039979393</v>
       </c>
       <c r="O2"/>
     </row>
@@ -517,10 +517,10 @@
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.584799554728351</v>
+        <v>0.584909831460181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.331392276581345</v>
+        <v>0.341342262719009</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -544,10 +544,10 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.577024484778259</v>
+        <v>0.580011888846628</v>
       </c>
       <c r="I4" t="n">
-        <v>0.33238972852208</v>
+        <v>0.297647797838728</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -555,7 +555,7 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.423205773841332</v>
+        <v>0.420219561881019</v>
       </c>
     </row>
   </sheetData>
@@ -606,13 +606,13 @@
         <v>0.377096382616238</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0320942684678203</v>
+        <v>0.0323602954567693</v>
       </c>
       <c r="E2" t="n">
-        <v>0.313141886300811</v>
+        <v>0.314690326070108</v>
       </c>
       <c r="F2" t="n">
-        <v>0.438412801294494</v>
+        <v>0.440503774564167</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -629,19 +629,19 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.339032003565788</v>
+        <v>0.346102039979393</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0516407500594495</v>
+        <v>0.0303530713098902</v>
       </c>
       <c r="E3" t="n">
-        <v>0.251630257505263</v>
+        <v>0.286015807819049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.44781872690609</v>
+        <v>0.410011192835733</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0000000000259809951330681</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>946</v>
@@ -655,16 +655,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.423205773841332</v>
+        <v>0.420219561881019</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0502264571493261</v>
+        <v>0.030186471621382</v>
       </c>
       <c r="E4" t="n">
-        <v>0.332552472256815</v>
+        <v>0.358961277303821</v>
       </c>
       <c r="F4" t="n">
-        <v>0.530268889581896</v>
+        <v>0.48063680907819</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -681,19 +681,19 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0841737702755438</v>
+        <v>0.0741175219016258</v>
       </c>
       <c r="D5" t="n">
-        <v>0.018194123510265</v>
+        <v>0.0147733175075226</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0498218903111359</v>
+        <v>0.0460440247358866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.120688704541321</v>
+        <v>0.100658447107308</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00000186014643799304</v>
+        <v>0.000000262442436005372</v>
       </c>
       <c r="H5" t="n">
         <v>946</v>
